--- a/NYT.xlsx
+++ b/NYT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F67FB4-4F93-4CBE-B274-82C3CAB66B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805EAF8F-0E57-4E09-9934-8ED630068C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{F0F54F86-B9EF-4E89-80C7-6F9BAE07501F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{F0F54F86-B9EF-4E89-80C7-6F9BAE07501F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>Oscar Settje</author>
   </authors>
   <commentList>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{17BE5044-A823-4CEB-8EBD-4B162FB14622}">
+    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{17BE5044-A823-4CEB-8EBD-4B162FB14622}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>NYT</t>
   </si>
@@ -258,18 +258,30 @@
   <si>
     <t>Ttoal Subs Growth</t>
   </si>
+  <si>
+    <t>Digital Only ARPU</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -345,26 +357,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -721,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>69.87</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -729,11 +747,11 @@
         <v>5</v>
       </c>
       <c r="H3" s="3">
-        <f>161.568285+0.780724</f>
-        <v>162.349009</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>45</v>
+        <f>160.457961+0.780724</f>
+        <v>161.238685</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -745,7 +763,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>11343.32525883</v>
+        <v>12979.714142500001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -756,11 +774,11 @@
         <v>7</v>
       </c>
       <c r="H5" s="3">
-        <f>249.339+368.013</f>
-        <v>617.35199999999998</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>45</v>
+        <f>255.445+386.712</f>
+        <v>642.15699999999993</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -770,8 +788,8 @@
       <c r="H6" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>45</v>
+      <c r="I6" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -780,7 +798,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>10725.973258829999</v>
+        <v>12337.557142500002</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F24A468-4260-4D44-8423-D91A08F99504}">
-  <dimension ref="A1:V206"/>
+  <dimension ref="A1:V208"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -888,14 +906,20 @@
       <c r="M3" s="3">
         <v>11760</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3">
+        <v>12210</v>
+      </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
+      <c r="T3" s="3">
+        <v>10820</v>
+      </c>
+      <c r="U3" s="3">
+        <v>12210</v>
+      </c>
       <c r="V3" s="3"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -923,14 +947,20 @@
       <c r="M4" s="3">
         <v>570</v>
       </c>
-      <c r="N4" s="3"/>
+      <c r="N4" s="3">
+        <v>570</v>
+      </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
+      <c r="T4" s="3">
+        <v>610</v>
+      </c>
+      <c r="U4" s="3">
+        <v>570</v>
+      </c>
       <c r="V4" s="3"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -963,109 +993,119 @@
         <f>+M3+M4</f>
         <v>12330</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="6">
+        <f>+N3+N4</f>
+        <v>12780</v>
+      </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
+      <c r="T5" s="6">
+        <f>+T3+T4</f>
+        <v>11430</v>
+      </c>
+      <c r="U5" s="6">
+        <f>+U3+U4</f>
+        <v>12780</v>
+      </c>
       <c r="V5" s="3"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
+      <c r="B6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15">
+        <v>9.42</v>
+      </c>
+      <c r="U6" s="15">
+        <v>9.68</v>
+      </c>
       <c r="V6" s="3"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>282.22800000000001</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>322.19799999999998</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
-        <v>367.44299999999998</v>
-      </c>
-      <c r="N7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>136.34899999999999</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>131.12899999999999</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="M8" s="2">
-        <v>127.187</v>
-      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3">
-        <v>418.577</v>
+        <v>282.22800000000001</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3">
-        <v>453.327</v>
+        <v>322.19799999999998</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3">
-        <v>494.63</v>
+        <v>367.44299999999998</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1073,768 +1113,897 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
+      <c r="T9" s="3">
+        <v>1254.5920000000001</v>
+      </c>
+      <c r="U9" s="3">
+        <v>1434.336</v>
+      </c>
       <c r="V9" s="3"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3">
-        <v>117.113</v>
+        <v>136.34899999999999</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3">
-        <v>118.37</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+        <v>131.12899999999999</v>
+      </c>
+      <c r="J10" s="4"/>
       <c r="M10" s="3">
-        <v>132.291</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+        <v>127.187</v>
+      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13">
+        <v>533.61500000000001</v>
+      </c>
+      <c r="U10" s="13">
+        <v>516.44200000000001</v>
+      </c>
+      <c r="V10" s="13"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
-        <v>62.655000000000001</v>
+        <v>418.577</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3">
-        <v>68.480999999999995</v>
+        <v>453.327</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>73.900000000000006</v>
+        <v>494.63</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
+      <c r="S11" s="3">
+        <v>1656.153</v>
+      </c>
+      <c r="T11" s="13">
+        <f>+T9+T10</f>
+        <v>1788.2070000000001</v>
+      </c>
+      <c r="U11" s="13">
+        <f>+U9+U10</f>
+        <v>1950.778</v>
+      </c>
       <c r="V11" s="3"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="6">
-        <f t="shared" ref="C12:H12" si="0">+SUM(C9:C11)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <f t="shared" si="0"/>
-        <v>598.34500000000003</v>
-      </c>
-      <c r="F12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <f>+SUM(I9:I11)</f>
-        <v>640.178</v>
-      </c>
-      <c r="J12" s="6">
-        <f t="shared" ref="J12:M12" si="1">+SUM(J9:J11)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" si="1"/>
-        <v>700.82100000000003</v>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
+        <v>117.113</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
+        <v>118.37</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3">
+        <v>132.291</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
+      <c r="S12" s="3">
+        <v>505.20600000000002</v>
+      </c>
+      <c r="T12" s="3">
+        <v>506.31099999999998</v>
+      </c>
+      <c r="U12" s="3">
+        <v>565.99300000000005</v>
+      </c>
       <c r="V12" s="3"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3">
-        <v>311.13499999999999</v>
+        <v>62.655000000000001</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3">
-        <v>331.839</v>
+        <v>68.480999999999995</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>349.07499999999999</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
+      <c r="S13" s="3">
+        <v>264.79300000000001</v>
+      </c>
+      <c r="T13" s="3">
+        <v>291.40100000000001</v>
+      </c>
+      <c r="U13" s="3">
+        <v>308.14699999999999</v>
+      </c>
       <c r="V13" s="3"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <f t="shared" ref="E14:H14" si="2">+E12-E13</f>
-        <v>287.21000000000004</v>
-      </c>
-      <c r="F14" s="3">
-        <f t="shared" si="2"/>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="6">
+        <f t="shared" ref="C14:H14" si="0">+SUM(C11:C13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="3">
-        <f t="shared" si="2"/>
+      <c r="D14" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <f t="shared" si="2"/>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>598.34500000000003</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <f>+I12-I13</f>
-        <v>308.339</v>
-      </c>
-      <c r="J14" s="3">
-        <f t="shared" ref="J14:M14" si="3">+J12-J13</f>
+      <c r="G14" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="3">
-        <f t="shared" si="3"/>
+      <c r="H14" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <f t="shared" si="3"/>
+      <c r="I14" s="6">
+        <f>+SUM(I11:I13)</f>
+        <v>640.178</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" ref="J14:M14" si="1">+SUM(J11:J13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="3">
-        <f t="shared" si="3"/>
-        <v>351.74600000000004</v>
+      <c r="K14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
+        <f t="shared" si="1"/>
+        <v>700.82100000000003</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+      <c r="S14" s="6">
+        <v>2426.152</v>
+      </c>
+      <c r="T14" s="6">
+        <v>2585.9189999999999</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2824.9180000000001</v>
+      </c>
       <c r="V14" s="3"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3">
-        <v>62.634999999999998</v>
+        <v>311.13499999999999</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3">
-        <v>69.131</v>
+        <v>331.839</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>79.576999999999998</v>
+        <v>349.07499999999999</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
+      <c r="S15" s="3">
+        <v>1249.0609999999999</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1309.5139999999999</v>
+      </c>
+      <c r="U15" s="3">
+        <v>1389.713</v>
+      </c>
       <c r="V15" s="3"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3">
-        <v>57.433</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+        <f t="shared" ref="E16:H16" si="2">+E14-E15</f>
+        <v>287.21000000000004</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="I16" s="3">
-        <v>61.03</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+        <f>+I14-I15</f>
+        <v>308.339</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" ref="J16:M16" si="3">+J14-J15</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M16" s="3">
-        <v>66.989000000000004</v>
+        <f t="shared" si="3"/>
+        <v>351.74600000000004</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
+      <c r="S16" s="3">
+        <f>+S14-S15</f>
+        <v>1177.0910000000001</v>
+      </c>
+      <c r="T16" s="3">
+        <f>+T14-T15</f>
+        <v>1276.405</v>
+      </c>
+      <c r="U16" s="3">
+        <f>+U14-U15</f>
+        <v>1435.2050000000002</v>
+      </c>
       <c r="V16" s="3"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3">
-        <v>81.87</v>
+        <v>62.634999999999998</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3">
-        <v>76.209000000000003</v>
+        <v>69.131</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3">
-        <v>76.64</v>
+        <v>79.576999999999998</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
+      <c r="S17" s="3">
+        <v>260.22699999999998</v>
+      </c>
+      <c r="T17" s="3">
+        <v>278.42500000000001</v>
+      </c>
+      <c r="U17" s="3">
+        <v>307.084</v>
+      </c>
       <c r="V17" s="3"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3">
-        <v>21.475000000000001</v>
+        <v>57.433</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <v>20.622</v>
+        <v>61.03</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3">
-        <v>21.341000000000001</v>
+        <v>66.989000000000004</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
+      <c r="S18" s="3">
+        <v>228.804</v>
+      </c>
+      <c r="T18" s="3">
+        <v>248.19800000000001</v>
+      </c>
+      <c r="U18" s="3">
+        <v>264.34699999999998</v>
+      </c>
       <c r="V18" s="3"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3">
-        <v>0</v>
+        <v>81.87</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <v>4.62</v>
+        <v>76.209000000000003</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3">
-        <v>2.411</v>
+        <v>76.64</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
+      <c r="S19" s="3">
+        <v>311.03899999999999</v>
+      </c>
+      <c r="T19" s="3">
+        <v>307.93</v>
+      </c>
+      <c r="U19" s="3">
+        <v>328.06400000000002</v>
+      </c>
       <c r="V19" s="3"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3">
-        <f>2.503-2.273</f>
-        <v>0.22999999999999998</v>
+        <v>21.475000000000001</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>20.622</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>21.341000000000001</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
+      <c r="S20" s="3">
+        <v>86.114999999999995</v>
+      </c>
+      <c r="T20" s="3">
+        <v>82.936000000000007</v>
+      </c>
+      <c r="U20" s="3">
+        <v>85.007000000000005</v>
+      </c>
       <c r="V20" s="3"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="3">
-        <f t="shared" ref="C21:H21" si="4">+C14-SUM(C15:C20)</f>
+        <v>27</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3">
         <v>0</v>
       </c>
-      <c r="D21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <f t="shared" si="4"/>
-        <v>63.567000000000064</v>
-      </c>
-      <c r="F21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
       <c r="I21" s="3">
-        <f>+I14-SUM(I15:I20)</f>
-        <v>76.726999999999975</v>
-      </c>
-      <c r="J21" s="3">
-        <f t="shared" ref="J21:M21" si="5">+J14-SUM(J15:J20)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <v>4.62</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
       <c r="M21" s="3">
-        <f t="shared" si="5"/>
-        <v>104.78800000000001</v>
+        <v>2.411</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="U21" s="3">
+        <v>13.321</v>
+      </c>
       <c r="V21" s="3"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3">
-        <v>0.68400000000000005</v>
+        <f>2.503-2.273</f>
+        <v>0.22999999999999998</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3">
-        <v>-4.649</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
+      <c r="S22" s="3">
+        <f>15.239-0.605</f>
+        <v>14.634</v>
+      </c>
+      <c r="T22" s="3">
+        <v>-2.98</v>
+      </c>
+      <c r="U22" s="3">
+        <f>2.858+2.967</f>
+        <v>5.8250000000000002</v>
+      </c>
       <c r="V22" s="3"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="C23" s="3">
+        <f t="shared" ref="C23:H23" si="4">+C16-SUM(C17:C22)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="E23" s="3">
-        <v>5.7359999999999998</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+        <f t="shared" si="4"/>
+        <v>63.567000000000064</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="I23" s="3">
-        <v>9.3659999999999997</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+        <f>+I16-SUM(I17:I22)</f>
+        <v>76.726999999999975</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" ref="J23:M23" si="5">+J16-SUM(J17:J22)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="M23" s="3">
-        <v>7.851</v>
+        <f t="shared" si="5"/>
+        <v>104.78800000000001</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
+      <c r="P23" s="3">
+        <f t="shared" ref="P23:U23" si="6">+P16-SUM(P17:P22)</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <f t="shared" si="6"/>
+        <v>276.27200000000016</v>
+      </c>
+      <c r="T23" s="3">
+        <f t="shared" si="6"/>
+        <v>351.09599999999989</v>
+      </c>
+      <c r="U23" s="3">
+        <f t="shared" si="6"/>
+        <v>431.5569999999999</v>
+      </c>
       <c r="V23" s="3"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" ref="C24:H24" si="6">+C21+SUM(C22:C23)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
       <c r="E24" s="3">
-        <f t="shared" si="6"/>
-        <v>69.987000000000066</v>
-      </c>
-      <c r="F24" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="3">
-        <f>+I21+SUM(I22:I23)</f>
-        <v>85.042999999999978</v>
-      </c>
-      <c r="J24" s="3">
-        <f t="shared" ref="J24:M24" si="7">+J21+SUM(J22:J23)</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+        <v>-1.05</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="3">
-        <f t="shared" si="7"/>
-        <v>107.99000000000001</v>
+        <v>-4.649</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
+      <c r="S24" s="3">
+        <f>2.737+2.477</f>
+        <v>5.2140000000000004</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-4.1580000000000004</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-18.556999999999999</v>
+      </c>
       <c r="V24" s="3"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3">
-        <v>16.372</v>
+        <v>5.7359999999999998</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3">
-        <v>20.9</v>
+        <v>9.3659999999999997</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3">
-        <v>26.352</v>
+        <v>7.851</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
+      <c r="S25" s="3">
+        <v>21.102</v>
+      </c>
+      <c r="T25" s="3">
+        <v>36.484999999999999</v>
+      </c>
+      <c r="U25" s="3">
+        <v>38.256</v>
+      </c>
       <c r="V25" s="3"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" ref="C26:H26" si="8">+C24-C25</f>
+        <f t="shared" ref="C26:H26" si="7">+C23+SUM(C24:C25)</f>
         <v>0</v>
       </c>
       <c r="D26" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="7"/>
+        <v>69.987000000000066</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f>+I23+SUM(I24:I25)</f>
+        <v>85.042999999999978</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" ref="J26:M26" si="8">+J23+SUM(J24:J25)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E26" s="3">
-        <f t="shared" si="8"/>
-        <v>53.615000000000066</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="L26" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G26" s="3">
+      <c r="M26" s="3">
         <f t="shared" si="8"/>
+        <v>107.99000000000001</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3">
+        <f t="shared" ref="P26:U26" si="9">+P23+SUM(P24:P25)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <f>+I24-I25</f>
-        <v>64.142999999999972</v>
-      </c>
-      <c r="J26" s="3">
-        <f t="shared" ref="J26:M26" si="9">+J24-J25</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="Q26" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L26" s="3">
+      <c r="R26" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M26" s="3">
+      <c r="S26" s="3">
         <f t="shared" si="9"/>
-        <v>81.638000000000005</v>
-      </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
+        <v>302.58800000000019</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" si="9"/>
+        <v>383.42299999999989</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="9"/>
+        <v>451.25599999999991</v>
+      </c>
       <c r="V26" s="3"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3">
+        <v>16.372</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3">
+        <v>20.9</v>
+      </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="M27" s="3">
+        <v>26.352</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
+      <c r="S27" s="3">
+        <f>69.836-0.365</f>
+        <v>69.471000000000004</v>
+      </c>
+      <c r="T27" s="3">
+        <v>89.597999999999999</v>
+      </c>
+      <c r="U27" s="3">
+        <v>107.27500000000001</v>
+      </c>
       <c r="V27" s="3"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="7" t="e">
-        <f t="shared" ref="C28:D28" si="10">+C26/C29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D28" s="7" t="e">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" ref="C28:H28" si="10">+C26-C27</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E28" s="7">
-        <f>+E26/E29</f>
-        <v>0.32579237761897856</v>
-      </c>
-      <c r="F28" s="7" t="e">
-        <f t="shared" ref="F28:M28" si="11">+F26/F29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="7" t="e">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="10"/>
+        <v>53.615000000000066</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <f>+I26-I27</f>
+        <v>64.142999999999972</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" ref="J28:M28" si="11">+J26-J27</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H28" s="7" t="e">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I28" s="7">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
         <f t="shared" si="11"/>
-        <v>0.3901191468139325</v>
-      </c>
-      <c r="J28" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L28" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M28" s="7">
-        <f t="shared" si="11"/>
-        <v>0.50077903595833695</v>
+        <v>81.638000000000005</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
+      <c r="P28" s="3">
+        <f t="shared" ref="P28:U28" si="12">+P26-P27</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <f t="shared" si="12"/>
+        <v>233.11700000000019</v>
+      </c>
+      <c r="T28" s="3">
+        <f t="shared" si="12"/>
+        <v>293.82499999999987</v>
+      </c>
+      <c r="U28" s="3">
+        <f t="shared" si="12"/>
+        <v>343.98099999999988</v>
+      </c>
       <c r="V28" s="3"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>164.56800000000001</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3">
-        <v>164.41900000000001</v>
-      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-      <c r="M29" s="3">
-        <v>163.02199999999999</v>
-      </c>
+      <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -1846,109 +2015,121 @@
       <c r="V29" s="3"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="B30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="7" t="e">
+        <f t="shared" ref="C30:D30" si="13">+C28/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D30" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E30" s="7">
+        <f>+E28/E31</f>
+        <v>0.32579237761897856</v>
+      </c>
+      <c r="F30" s="7" t="e">
+        <f t="shared" ref="F30:M30" si="14">+F28/F31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="14"/>
+        <v>0.3901191468139325</v>
+      </c>
+      <c r="J30" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L30" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="14"/>
+        <v>0.50077903595833695</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
+      <c r="S30" s="7">
+        <f t="shared" ref="S30:T30" si="15">+S28/S31</f>
+        <v>1.4152233170026904</v>
+      </c>
+      <c r="T30" s="7">
+        <f t="shared" si="15"/>
+        <v>1.7869849475444723</v>
+      </c>
+      <c r="U30" s="7">
+        <f>+U28/U31</f>
+        <v>2.1082822067088745</v>
+      </c>
       <c r="V30" s="3"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B31" s="9" t="s">
-        <v>59</v>
+      <c r="B31" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3">
+        <v>164.56800000000001</v>
+      </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="8" t="e">
-        <f>+G3/C3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H31" s="8" t="e">
-        <f>+H3/D3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I31" s="8" t="e">
-        <f>+I3/E3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" s="8" t="e">
-        <f>+J3/F3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="8" t="e">
-        <f>+K3/G3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L31" s="8" t="e">
-        <f>+L3/H3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="8">
-        <f>+M3/I3-1</f>
-        <v>0.12320916905444124</v>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3">
+        <v>164.41900000000001</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3">
+        <v>163.02199999999999</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
+      <c r="S31" s="3">
+        <v>164.721</v>
+      </c>
+      <c r="T31" s="3">
+        <v>164.42500000000001</v>
+      </c>
+      <c r="U31" s="3">
+        <v>163.15700000000001</v>
+      </c>
       <c r="V31" s="3"/>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B32" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="8" t="e">
-        <f>+G4/C4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H32" s="8" t="e">
-        <f>+H4/D4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="8" t="e">
-        <f>+I4/E4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J32" s="8" t="e">
-        <f>+J4/F4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="8" t="e">
-        <f>+K4/G4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L32" s="8" t="e">
-        <f>+L4/H4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="8">
-        <f>+M4/I4-1</f>
-        <v>-8.064516129032262E-2</v>
-      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -1961,39 +2142,39 @@
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="8" t="e">
-        <f>+G5/C5-1</f>
+        <f>+G3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H33" s="8" t="e">
-        <f>+H5/D5-1</f>
+        <f>+H3/D3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I33" s="8" t="e">
-        <f>+I5/E5-1</f>
+        <f>+I3/E3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="8" t="e">
-        <f>+J5/F5-1</f>
+        <f>+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="8" t="e">
-        <f>+K5/G5-1</f>
+        <f>+K3/G3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L33" s="8" t="e">
-        <f>+L5/H5-1</f>
+        <f>+L3/H3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M33" s="8">
-        <f>+M5/I5-1</f>
-        <v>0.11181244364292153</v>
+        <f>+M3/I3-1</f>
+        <v>0.12320916905444124</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -2001,334 +2182,358 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
+      <c r="T33" s="8" t="e">
+        <f>+T3/S3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="8">
+        <f>+U3/T3-1</f>
+        <v>0.1284658040665434</v>
+      </c>
       <c r="V33" s="3"/>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="8" t="e">
-        <f t="shared" ref="G34:H37" si="12">+G9/C9-1</f>
+        <f>+G4/C4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H34" s="8" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="8">
-        <f>+I9/E9-1</f>
-        <v>8.3019372779679745E-2</v>
+        <f>+H4/D4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I34" s="8" t="e">
+        <f>+I4/E4-1</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="J34" s="8" t="e">
-        <f t="shared" ref="J34:N37" si="13">+J9/F9-1</f>
+        <f>+J4/F4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+K4/G4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L34" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+L4/H4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M34" s="8">
-        <f t="shared" si="13"/>
-        <v>9.1110831695442762E-2</v>
-      </c>
-      <c r="N34" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>+M4/I4-1</f>
+        <v>-8.064516129032262E-2</v>
+      </c>
+      <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
+      <c r="T34" s="8" t="e">
+        <f>+T4/S4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="8">
+        <f>+U4/T4-1</f>
+        <v>-6.557377049180324E-2</v>
+      </c>
       <c r="V34" s="3"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f>+G5/C5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="8" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I35" s="8">
-        <f t="shared" ref="I35:I37" si="14">+I10/E10-1</f>
-        <v>1.0733223467932707E-2</v>
+        <f>+H5/D5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I35" s="8" t="e">
+        <f>+I5/E5-1</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="J35" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+J5/F5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+K5/G5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L35" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f>+L5/H5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" si="13"/>
-        <v>0.11760581228351774</v>
-      </c>
-      <c r="N35" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>+M5/I5-1</f>
+        <v>0.11181244364292153</v>
+      </c>
+      <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
+      <c r="T35" s="8" t="e">
+        <f>+T5/S5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" s="8">
+        <f>+U5/T5-1</f>
+        <v>0.11811023622047245</v>
+      </c>
       <c r="V35" s="3"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G36:H39" si="16">+G11/C11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H36" s="8" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="14"/>
-        <v>9.2985396217380778E-2</v>
+        <f>+I11/E11-1</f>
+        <v>8.3019372779679745E-2</v>
       </c>
       <c r="J36" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J36:N39" si="17">+J11/F11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M36" s="8">
-        <f t="shared" si="13"/>
-        <v>7.9131437917086656E-2</v>
+        <f t="shared" si="17"/>
+        <v>9.1110831695442762E-2</v>
       </c>
       <c r="N36" s="8" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
+      <c r="S36" s="8" t="e">
+        <f>+S11/R11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" s="8">
+        <f>+T11/S11-1</f>
+        <v>7.9735386766802474E-2</v>
+      </c>
+      <c r="U36" s="8">
+        <f>+U11/T11-1</f>
+        <v>9.0912852930337351E-2</v>
+      </c>
       <c r="V36" s="3"/>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="11" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H37" s="11" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I37" s="11">
-        <f t="shared" si="14"/>
-        <v>6.9914514201672828E-2</v>
-      </c>
-      <c r="J37" s="11" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="11" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L37" s="11" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M37" s="11">
-        <f t="shared" si="13"/>
-        <v>9.4728341180109421E-2</v>
-      </c>
-      <c r="N37" s="11" t="e">
-        <f t="shared" si="13"/>
+      <c r="B37" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="8" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H37" s="8" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" ref="I37:I39" si="18">+I12/E12-1</f>
+        <v>1.0733223467932707E-2</v>
+      </c>
+      <c r="J37" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K37" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L37" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M37" s="8">
+        <f t="shared" si="17"/>
+        <v>0.11760581228351774</v>
+      </c>
+      <c r="N37" s="8" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
+      <c r="S37" s="8" t="e">
+        <f>+S12/R12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T37" s="8">
+        <f>+T12/S12-1</f>
+        <v>2.1872265966753623E-3</v>
+      </c>
+      <c r="U37" s="8">
+        <f>+U12/T12-1</f>
+        <v>0.11787616701987536</v>
+      </c>
       <c r="V37" s="3"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="8" t="e">
-        <f t="shared" ref="C38:H38" si="15">+C14/C12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D38" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="8">
-        <f t="shared" si="15"/>
-        <v>0.48000735361706043</v>
-      </c>
-      <c r="F38" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="B38" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="8" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="8" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="8">
-        <f>+I14/I12</f>
-        <v>0.48164572978140452</v>
+        <f t="shared" si="18"/>
+        <v>9.2985396217380778E-2</v>
       </c>
       <c r="J38" s="8" t="e">
-        <f t="shared" ref="J38:N38" si="16">+J14/J12</f>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K38" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" si="16"/>
-        <v>0.50190562212034173</v>
+        <f t="shared" si="17"/>
+        <v>7.9131437917086656E-2</v>
       </c>
       <c r="N38" s="8" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
+      <c r="S38" s="8" t="e">
+        <f>+S13/R13-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T38" s="8">
+        <f>+T13/S13-1</f>
+        <v>0.10048604003882278</v>
+      </c>
+      <c r="U38" s="8">
+        <f>+U13/T13-1</f>
+        <v>5.7467201553872416E-2</v>
+      </c>
       <c r="V38" s="3"/>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="8" t="e">
-        <f t="shared" ref="C39:H39" si="17">+C21/C12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D39" s="8" t="e">
+      <c r="B39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="11" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H39" s="11" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I39" s="11">
+        <f t="shared" si="18"/>
+        <v>6.9914514201672828E-2</v>
+      </c>
+      <c r="J39" s="11" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E39" s="8">
+      <c r="K39" s="11" t="e">
         <f t="shared" si="17"/>
-        <v>0.10623803992679819</v>
-      </c>
-      <c r="F39" s="8" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L39" s="11" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G39" s="8" t="e">
+      <c r="M39" s="11">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H39" s="8" t="e">
+        <v>9.4728341180109421E-2</v>
+      </c>
+      <c r="N39" s="11" t="e">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I39" s="8">
-        <f>+I21/I12</f>
-        <v>0.11985260349465301</v>
-      </c>
-      <c r="J39" s="8" t="e">
-        <f t="shared" ref="J39:N39" si="18">+J21/J12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K39" s="8" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L39" s="8" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M39" s="8">
-        <f t="shared" si="18"/>
-        <v>0.14952177517511606</v>
-      </c>
-      <c r="N39" s="8" t="e">
-        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
+      <c r="S39" s="11" t="e">
+        <f>+S14/R14-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" s="11">
+        <f>+T14/S14-1</f>
+        <v>6.5852015867101432E-2</v>
+      </c>
+      <c r="U39" s="11">
+        <f>+U14/T14-1</f>
+        <v>9.2423235221211542E-2</v>
+      </c>
       <c r="V39" s="3"/>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C40" s="8" t="e">
-        <f t="shared" ref="C40:H40" si="19">+C25/C24</f>
+        <f t="shared" ref="C40:H40" si="19">+C16/C14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D40" s="8" t="e">
@@ -2337,7 +2542,7 @@
       </c>
       <c r="E40" s="8">
         <f t="shared" si="19"/>
-        <v>0.23392915827225033</v>
+        <v>0.48000735361706043</v>
       </c>
       <c r="F40" s="8" t="e">
         <f t="shared" si="19"/>
@@ -2352,11 +2557,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I40" s="8">
-        <f>+I25/I24</f>
-        <v>0.2457580282915702</v>
+        <f>+I16/I14</f>
+        <v>0.48164572978140452</v>
       </c>
       <c r="J40" s="8" t="e">
-        <f t="shared" ref="J40:N40" si="20">+J25/J24</f>
+        <f t="shared" ref="J40:N40" si="20">+J16/J14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K40" s="8" t="e">
@@ -2369,7 +2574,7 @@
       </c>
       <c r="M40" s="8">
         <f t="shared" si="20"/>
-        <v>0.24402259468469301</v>
+        <v>0.50190562212034173</v>
       </c>
       <c r="N40" s="8" t="e">
         <f t="shared" si="20"/>
@@ -2379,53 +2584,158 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
+      <c r="S40" s="8">
+        <f t="shared" ref="S40" si="21">+S16/S14</f>
+        <v>0.48516787076819595</v>
+      </c>
+      <c r="T40" s="8">
+        <f t="shared" ref="T40:U40" si="22">+T16/T14</f>
+        <v>0.49359821401985138</v>
+      </c>
+      <c r="U40" s="8">
+        <f t="shared" si="22"/>
+        <v>0.50805191513523584</v>
+      </c>
       <c r="V40" s="3"/>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="8" t="e">
+        <f t="shared" ref="C41:H41" si="23">+C23/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D41" s="8" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E41" s="8">
+        <f t="shared" si="23"/>
+        <v>0.10623803992679819</v>
+      </c>
+      <c r="F41" s="8" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G41" s="8" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H41" s="8" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I41" s="8">
+        <f>+I23/I14</f>
+        <v>0.11985260349465301</v>
+      </c>
+      <c r="J41" s="8" t="e">
+        <f t="shared" ref="J41:N41" si="24">+J23/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K41" s="8" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L41" s="8" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M41" s="8">
+        <f t="shared" si="24"/>
+        <v>0.14952177517511606</v>
+      </c>
+      <c r="N41" s="8" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
+      <c r="S41" s="8">
+        <f t="shared" ref="S41" si="25">+S23/S14</f>
+        <v>0.11387250262967867</v>
+      </c>
+      <c r="T41" s="8">
+        <f t="shared" ref="T41:U41" si="26">+T23/T14</f>
+        <v>0.13577223416510723</v>
+      </c>
+      <c r="U41" s="8">
+        <f t="shared" si="26"/>
+        <v>0.15276797415004609</v>
+      </c>
       <c r="V41" s="3"/>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="B42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="8" t="e">
+        <f t="shared" ref="C42:H42" si="27">+C27/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D42" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E42" s="8">
+        <f t="shared" si="27"/>
+        <v>0.23392915827225033</v>
+      </c>
+      <c r="F42" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G42" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H42" s="8" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I42" s="8">
+        <f>+I27/I26</f>
+        <v>0.2457580282915702</v>
+      </c>
+      <c r="J42" s="8" t="e">
+        <f t="shared" ref="J42:N42" si="28">+J27/J26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K42" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L42" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M42" s="8">
+        <f t="shared" si="28"/>
+        <v>0.24402259468469301</v>
+      </c>
+      <c r="N42" s="8" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
+      <c r="S42" s="8">
+        <f t="shared" ref="S42" si="29">+S27/S26</f>
+        <v>0.22958940870093975</v>
+      </c>
+      <c r="T42" s="8">
+        <f t="shared" ref="T42:U42" si="30">+T27/T26</f>
+        <v>0.23367925241834742</v>
+      </c>
+      <c r="U42" s="8">
+        <f t="shared" si="30"/>
+        <v>0.23772537096459664</v>
+      </c>
       <c r="V42" s="3"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.2">
@@ -6036,6 +6346,50 @@
       <c r="U206" s="3"/>
       <c r="V206" s="3"/>
     </row>
+    <row r="207" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="3"/>
+      <c r="F207" s="3"/>
+      <c r="G207" s="3"/>
+      <c r="H207" s="3"/>
+      <c r="I207" s="3"/>
+      <c r="J207" s="3"/>
+      <c r="K207" s="3"/>
+      <c r="L207" s="3"/>
+      <c r="M207" s="3"/>
+      <c r="N207" s="3"/>
+      <c r="O207" s="3"/>
+      <c r="P207" s="3"/>
+      <c r="Q207" s="3"/>
+      <c r="R207" s="3"/>
+      <c r="S207" s="3"/>
+      <c r="T207" s="3"/>
+      <c r="U207" s="3"/>
+      <c r="V207" s="3"/>
+    </row>
+    <row r="208" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+      <c r="I208" s="3"/>
+      <c r="J208" s="3"/>
+      <c r="K208" s="3"/>
+      <c r="L208" s="3"/>
+      <c r="M208" s="3"/>
+      <c r="N208" s="3"/>
+      <c r="O208" s="3"/>
+      <c r="P208" s="3"/>
+      <c r="Q208" s="3"/>
+      <c r="R208" s="3"/>
+      <c r="S208" s="3"/>
+      <c r="T208" s="3"/>
+      <c r="U208" s="3"/>
+      <c r="V208" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{5649D24E-83E0-4D00-976A-B7A06201555C}"/>
